--- a/data/trans_dic/P64D$noloshace_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,09</t>
+          <t>1,31; 5,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 7,66</t>
+          <t>2,77; 7,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,21</t>
+          <t>2,5; 5,49</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 4,12</t>
+          <t>0,7; 4,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,26</t>
+          <t>1,55; 4,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,79</t>
+          <t>1,1; 3,72</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,28</t>
+          <t>1,28; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 4,8</t>
+          <t>1,21; 4,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,19</t>
+          <t>1,54; 4,06</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 10,96</t>
+          <t>5,63; 11,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,48</t>
+          <t>2,75; 6,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 8,16</t>
+          <t>4,4; 8,13</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 4,97</t>
+          <t>2,47; 5,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,53</t>
+          <t>2,74; 4,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 4,44</t>
+          <t>2,78; 4,44</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios</t>
+          <t>Población que no realiza trayectos desde su casa al centro de trabajo/estudios (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4909; 16947</t>
+          <t>4353; 17700</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7168; 19763</t>
+          <t>7136; 19312</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13437; 30806</t>
+          <t>14772; 32477</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4526; 33181</t>
+          <t>5643; 35411</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6739; 17075</t>
+          <t>6217; 17005</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13514; 45705</t>
+          <t>13255; 44906</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4583; 18782</t>
+          <t>4550; 18172</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3822; 15484</t>
+          <t>3893; 15342</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10973; 28417</t>
+          <t>10428; 27575</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26311; 51634</t>
+          <t>26536; 53098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12397; 31091</t>
+          <t>13203; 32612</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43318; 77553</t>
+          <t>41874; 77272</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>48000; 97633</t>
+          <t>48465; 99132</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38912; 66157</t>
+          <t>40003; 66794</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96243; 151993</t>
+          <t>95297; 152098</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$noloshace_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P64D$noloshace_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,31</t>
+          <t>1,66; 6,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,77; 7,48</t>
+          <t>3,18; 7,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,49</t>
+          <t>2,73; 5,87</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,4</t>
+          <t>1,48; 4,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,24</t>
+          <t>1,92; 4,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,72</t>
+          <t>2,04; 4,34</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,1</t>
+          <t>1,52; 5,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,76</t>
+          <t>1,28; 4,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,06</t>
+          <t>1,74; 4,34</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 11,27</t>
+          <t>5,91; 11,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,8</t>
+          <t>3,96; 7,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 8,13</t>
+          <t>5,57; 8,97</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,04</t>
+          <t>3,48; 5,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,57</t>
+          <t>3,27; 5,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 4,44</t>
+          <t>3,67; 5,15</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>12053</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>26392</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4353; 17700</t>
+          <t>6104; 23008</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7136; 19312</t>
+          <t>8870; 21756</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14772; 32477</t>
+          <t>17645; 37909</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17912</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>10645</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>32241</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5643; 35411</t>
+          <t>9291; 30327</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6217; 17005</t>
+          <t>8568; 21293</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13255; 44906</t>
+          <t>21918; 46682</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9570</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>21818</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4550; 18172</t>
+          <t>6360; 21508</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3893; 15342</t>
+          <t>4323; 15623</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10428; 27575</t>
+          <t>13133; 32739</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37708</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21565</t>
+          <t>25294</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>68401</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26536; 53098</t>
+          <t>30558; 60961</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13203; 32612</t>
+          <t>17733; 34918</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41874; 77272</t>
+          <t>53761; 86486</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73386</t>
+          <t>86023</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>52237</t>
+          <t>62829</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>125623</t>
+          <t>148852</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>48465; 99132</t>
+          <t>67045; 108552</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40003; 66794</t>
+          <t>49386; 77749</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>95297; 152098</t>
+          <t>126351; 177170</t>
         </is>
       </c>
     </row>
